--- a/Results_experiment/exp_5/preds_1111122222333222.xlsx
+++ b/Results_experiment/exp_5/preds_1111122222333222.xlsx
@@ -660,7 +660,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D2">
-        <v>1.262826800346375</v>
+        <v>2.152294397354126</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -674,7 +674,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D3">
-        <v>1.746957182884216</v>
+        <v>1.526046991348267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.7138994932174683</v>
+        <v>2.078404188156128</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -702,7 +702,7 @@
         <v>8.5</v>
       </c>
       <c r="D5">
-        <v>7.016051769256592</v>
+        <v>7.584072113037109</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -716,7 +716,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D6">
-        <v>8.030800819396973</v>
+        <v>5.203371047973633</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -730,7 +730,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>4.123757839202881</v>
+        <v>1.376951098442078</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -744,7 +744,7 @@
         <v>9.5</v>
       </c>
       <c r="D8">
-        <v>0.9861519336700439</v>
+        <v>3.927588224411011</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -758,7 +758,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D9">
-        <v>5.5815749168396</v>
+        <v>3.7326819896698</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -772,7 +772,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D10">
-        <v>2.371421575546265</v>
+        <v>1.520702600479126</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -786,7 +786,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D11">
-        <v>6.674726963043213</v>
+        <v>1.549070119857788</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -800,7 +800,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>3.243603706359863</v>
+        <v>2.304839849472046</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -814,7 +814,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D13">
-        <v>1.076484680175781</v>
+        <v>2.023715019226074</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -828,7 +828,7 @@
         <v>0.5</v>
       </c>
       <c r="D14">
-        <v>1.428977131843567</v>
+        <v>2.302461862564087</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -842,7 +842,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D15">
-        <v>1.089508771896362</v>
+        <v>1.878127574920654</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -856,7 +856,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D16">
-        <v>1.110145688056946</v>
+        <v>1.922958850860596</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -870,7 +870,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D17">
-        <v>4.617757320404053</v>
+        <v>1.569583177566528</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -884,7 +884,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D18">
-        <v>3.682422876358032</v>
+        <v>2.302136659622192</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -898,7 +898,7 @@
         <v>25.79999923706055</v>
       </c>
       <c r="D19">
-        <v>18.06985092163086</v>
+        <v>20.13552474975586</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -912,7 +912,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D20">
-        <v>1.071323156356812</v>
+        <v>1.495555758476257</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -926,7 +926,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D21">
-        <v>13.60271835327148</v>
+        <v>8.176108360290527</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -940,7 +940,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D22">
-        <v>18.75427436828613</v>
+        <v>17.51094436645508</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -954,7 +954,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D23">
-        <v>0.9695966839790344</v>
+        <v>1.61149525642395</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -968,7 +968,7 @@
         <v>13.89999961853027</v>
       </c>
       <c r="D24">
-        <v>7.636643409729004</v>
+        <v>8.200758934020996</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -982,7 +982,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D25">
-        <v>1.0118328332901</v>
+        <v>2.138721466064453</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -996,7 +996,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D26">
-        <v>0.9753835201263428</v>
+        <v>2.03800892829895</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1010,7 +1010,7 @@
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>0.9687346220016479</v>
+        <v>1.840502977371216</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1024,7 +1024,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D28">
-        <v>1.119083285331726</v>
+        <v>2.453824281692505</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1038,7 +1038,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D29">
-        <v>1.394175410270691</v>
+        <v>2.364391803741455</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1052,7 +1052,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D30">
-        <v>4.659887790679932</v>
+        <v>5.291600227355957</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1066,7 +1066,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D31">
-        <v>15.89674854278564</v>
+        <v>16.01447677612305</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1080,7 +1080,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D32">
-        <v>1.5787113904953</v>
+        <v>2.250398635864258</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1094,7 +1094,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D33">
-        <v>0.6719103455543518</v>
+        <v>1.711052775382996</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1108,7 +1108,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D34">
-        <v>1.59839928150177</v>
+        <v>2.700109720230103</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1122,7 +1122,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D35">
-        <v>7.426382541656494</v>
+        <v>7.020623207092285</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1136,7 +1136,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D36">
-        <v>7.948524951934814</v>
+        <v>8.30455493927002</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="D37">
-        <v>15.2303466796875</v>
+        <v>15.79044246673584</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1164,7 +1164,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D38">
-        <v>0.9123778343200684</v>
+        <v>2.814692735671997</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1178,7 +1178,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D39">
-        <v>3.255065679550171</v>
+        <v>1.514957070350647</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1192,7 +1192,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D40">
-        <v>0.8967869877815247</v>
+        <v>1.527508139610291</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1206,7 +1206,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D41">
-        <v>8.103358268737793</v>
+        <v>9.75971794128418</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1220,7 +1220,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>0.8868942260742188</v>
+        <v>1.935166001319885</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1234,7 +1234,7 @@
         <v>9.5</v>
       </c>
       <c r="D43">
-        <v>0.7440319657325745</v>
+        <v>1.581931352615356</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1248,7 +1248,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D44">
-        <v>2.311048746109009</v>
+        <v>2.452816724777222</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1262,7 +1262,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="D45">
-        <v>8.341659545898438</v>
+        <v>9.447245597839355</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1276,7 +1276,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>0.8578664064407349</v>
+        <v>1.444637775421143</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1290,7 +1290,7 @@
         <v>10.5</v>
       </c>
       <c r="D47">
-        <v>0.7166846394538879</v>
+        <v>1.497826099395752</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1304,7 +1304,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D48">
-        <v>0.8973895907402039</v>
+        <v>1.785120010375977</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1318,7 +1318,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D49">
-        <v>0.6412619352340698</v>
+        <v>1.471791625022888</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1332,7 +1332,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D50">
-        <v>1.207825541496277</v>
+        <v>2.190915107727051</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1346,7 +1346,7 @@
         <v>3</v>
       </c>
       <c r="D51">
-        <v>1.671693086624146</v>
+        <v>2.644421339035034</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1360,7 +1360,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D52">
-        <v>1.250381708145142</v>
+        <v>2.19246244430542</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1374,7 +1374,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D53">
-        <v>9.091991424560547</v>
+        <v>11.6265172958374</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1388,7 +1388,7 @@
         <v>28.20000076293945</v>
       </c>
       <c r="D54">
-        <v>15.58608913421631</v>
+        <v>17.90446281433105</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1402,7 +1402,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D55">
-        <v>7.002190113067627</v>
+        <v>7.4420166015625</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1416,7 +1416,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D56">
-        <v>3.112334012985229</v>
+        <v>1.919520735740662</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1430,7 +1430,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D57">
-        <v>1.129900693893433</v>
+        <v>2.001129150390625</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1444,7 +1444,7 @@
         <v>8.5</v>
       </c>
       <c r="D58">
-        <v>9.346363067626953</v>
+        <v>9.975614547729492</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1458,7 +1458,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D59">
-        <v>8.7884521484375</v>
+        <v>9.318653106689453</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1472,7 +1472,7 @@
         <v>7.5</v>
       </c>
       <c r="D60">
-        <v>3.943889379501343</v>
+        <v>3.769299745559692</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1486,7 +1486,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D61">
-        <v>4.941112995147705</v>
+        <v>1.552792072296143</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1500,7 +1500,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D62">
-        <v>2.776873350143433</v>
+        <v>1.324898242950439</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1514,7 +1514,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D63">
-        <v>1.086730241775513</v>
+        <v>1.875932216644287</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1528,7 +1528,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D64">
-        <v>1.360888838768005</v>
+        <v>2.188721179962158</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1542,7 +1542,7 @@
         <v>26.70000076293945</v>
       </c>
       <c r="D65">
-        <v>16.12850189208984</v>
+        <v>17.90416526794434</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1556,7 +1556,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D66">
-        <v>1.111249923706055</v>
+        <v>2.275923728942871</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1570,7 +1570,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D67">
-        <v>11.92729377746582</v>
+        <v>11.89096546173096</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1584,7 +1584,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D68">
-        <v>1.126827001571655</v>
+        <v>2.057482004165649</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1598,7 +1598,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D69">
-        <v>1.163748860359192</v>
+        <v>1.738948583602905</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1612,7 +1612,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D70">
-        <v>1.118965625762939</v>
+        <v>1.356438636779785</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1626,7 +1626,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D71">
-        <v>6.8073410987854</v>
+        <v>1.753504276275635</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1640,7 +1640,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D72">
-        <v>1.079460978507996</v>
+        <v>1.350262403488159</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1654,7 +1654,7 @@
         <v>3.5</v>
       </c>
       <c r="D73">
-        <v>1.117253661155701</v>
+        <v>2.817817449569702</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1668,7 +1668,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D74">
-        <v>5.059718608856201</v>
+        <v>2.50403881072998</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1682,7 +1682,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D75">
-        <v>1.03543496131897</v>
+        <v>1.46343207359314</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1696,7 +1696,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D76">
-        <v>1.249911189079285</v>
+        <v>2.234088182449341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1710,7 +1710,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D77">
-        <v>1.389870405197144</v>
+        <v>2.499526739120483</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1724,7 +1724,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D78">
-        <v>1.003772497177124</v>
+        <v>1.882331371307373</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1738,7 +1738,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D79">
-        <v>15.14599418640137</v>
+        <v>12.74595642089844</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1752,7 +1752,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D80">
-        <v>2.032588005065918</v>
+        <v>1.576219081878662</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="D81">
-        <v>1.533404111862183</v>
+        <v>2.15004563331604</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1780,7 +1780,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D82">
-        <v>0.7715281844139099</v>
+        <v>1.757735729217529</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>0.8293731808662415</v>
+        <v>2.078881740570068</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1808,7 +1808,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D84">
-        <v>5.617837429046631</v>
+        <v>5.369239807128906</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1822,7 +1822,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D85">
-        <v>10.1831226348877</v>
+        <v>11.51348209381104</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1836,7 +1836,7 @@
         <v>2.5</v>
       </c>
       <c r="D86">
-        <v>1.467879295349121</v>
+        <v>1.593767642974854</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1850,7 +1850,7 @@
         <v>0.5</v>
       </c>
       <c r="D87">
-        <v>1.283557534217834</v>
+        <v>2.144906997680664</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1864,7 +1864,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D88">
-        <v>0.9695244431495667</v>
+        <v>2.941163539886475</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1878,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>1.161849737167358</v>
+        <v>1.896923303604126</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1892,7 +1892,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D90">
-        <v>5.347558498382568</v>
+        <v>2.153826713562012</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1906,7 +1906,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D91">
-        <v>0.9334677457809448</v>
+        <v>2.030393123626709</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1920,7 +1920,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D92">
-        <v>0.826922595500946</v>
+        <v>1.556934595108032</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1934,7 +1934,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D93">
-        <v>0.9372386932373047</v>
+        <v>2.33303165435791</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1948,7 +1948,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>6.80319356918335</v>
+        <v>2.104795455932617</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1962,7 +1962,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D95">
-        <v>1.546752095222473</v>
+        <v>2.625399351119995</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1976,7 +1976,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D96">
-        <v>0.7770941853523254</v>
+        <v>2.673809766769409</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1990,7 +1990,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D97">
-        <v>4.94977855682373</v>
+        <v>5.314690589904785</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2004,7 +2004,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D98">
-        <v>8.00196647644043</v>
+        <v>7.919958114624023</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2018,7 +2018,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D99">
-        <v>0.8057451844215393</v>
+        <v>1.493714928627014</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2032,7 +2032,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D100">
-        <v>0.7524222731590271</v>
+        <v>1.803468108177185</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2046,7 +2046,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D101">
-        <v>14.31307315826416</v>
+        <v>16.54807281494141</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2060,7 +2060,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D102">
-        <v>1.457744002342224</v>
+        <v>2.639500379562378</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2074,7 +2074,7 @@
         <v>12.5</v>
       </c>
       <c r="D103">
-        <v>8.124326705932617</v>
+        <v>8.917017936706543</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2088,7 +2088,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D104">
-        <v>4.338243961334229</v>
+        <v>5.279340744018555</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2102,7 +2102,7 @@
         <v>17.60000038146973</v>
       </c>
       <c r="D105">
-        <v>9.208437919616699</v>
+        <v>1.389594793319702</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2116,7 +2116,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>0.9524094462394714</v>
+        <v>2.237460136413574</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2130,7 +2130,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D107">
-        <v>1.414393901824951</v>
+        <v>2.419510364532471</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2144,7 +2144,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>1.393041729927063</v>
+        <v>2.488630056381226</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2158,7 +2158,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D109">
-        <v>6.990014553070068</v>
+        <v>1.805389523506165</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2172,7 +2172,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D110">
-        <v>0.8351900577545166</v>
+        <v>1.872962236404419</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2186,7 +2186,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D111">
-        <v>6.895551204681396</v>
+        <v>6.131345748901367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2200,7 +2200,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D112">
-        <v>1.155409812927246</v>
+        <v>2.043326139450073</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2214,7 +2214,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D113">
-        <v>1.18758487701416</v>
+        <v>1.976891398429871</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2228,7 +2228,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D114">
-        <v>8.243320465087891</v>
+        <v>7.228130340576172</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2242,7 +2242,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D115">
-        <v>7.430519104003906</v>
+        <v>5.289997100830078</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2256,7 +2256,7 @@
         <v>39.70000076293945</v>
       </c>
       <c r="D116">
-        <v>0.8141114711761475</v>
+        <v>1.291784048080444</v>
       </c>
     </row>
   </sheetData>
